--- a/xlsx/packagedata template-alt1.xlsx
+++ b/xlsx/packagedata template-alt1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2725A9F-08A7-47FF-971D-BB63D92F4665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB4597C-313F-4834-A58E-FC36D77DB8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>双向可叉</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,10 +110,6 @@
   </si>
   <si>
     <t>LSA443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -550,7 +546,7 @@
         <v>69</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2">
         <v>32</v>
@@ -562,7 +558,7 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
@@ -580,7 +576,7 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -594,7 +590,7 @@
         <v>69</v>
       </c>
       <c r="D3">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -606,7 +602,7 @@
         <v>18</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -624,7 +620,7 @@
         <v>14</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -650,7 +646,7 @@
         <v>19</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
@@ -668,7 +664,7 @@
         <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
